--- a/data/raw/Video.xlsx
+++ b/data/raw/Video.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/daschland-scripts/data/spreadsheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noraammann/Documents/Cloned_GitHub/daschland-scripts/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E99E8C2-A6A9-9A4D-A8F0-F3F4A97FAF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1AAB8E-D114-684A-B74A-F4AFB2AF3A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="46600" windowHeight="30200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -103,6 +102,12 @@
   </si>
   <si>
     <t>Noémi Villars-Amberg, Daniela Subotic</t>
+  </si>
+  <si>
+    <t>Wikidata Link</t>
+  </si>
+  <si>
+    <t>https://www.wikidata.org/wiki/Q2302672</t>
   </si>
 </sst>
 </file>
@@ -386,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.5" customWidth="1"/>
@@ -399,7 +404,7 @@
     <col min="10" max="10" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,8 +435,11 @@
       <c r="J1" s="8" t="s">
         <v>18</v>
       </c>
+      <c r="K1" s="8" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -462,10 +470,13 @@
       <c r="J2" s="8" t="s">
         <v>19</v>
       </c>
+      <c r="K2" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" ht="152.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:10" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:11" ht="152.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.51180555555555596"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
